--- a/estudo-mercado-gtk/dossie-bnb/previsao-faturamento.xlsx
+++ b/estudo-mercado-gtk/dossie-bnb/previsao-faturamento.xlsx
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>35574.95</v>
+        <v>31306.61</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>60477.41</v>
+        <v>53221.24</v>
       </c>
       <c r="D11" s="6" t="inlineStr"/>
     </row>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>114324.08</v>
+        <v>105323.8</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>172061.83</v>
+        <v>152433.9</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>228025.11</v>
+        <v>207193.44</v>
       </c>
       <c r="D14" s="6" t="inlineStr"/>
     </row>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>265671.99</v>
+        <v>267659.98</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>296439.78</v>
+        <v>304799.16</v>
       </c>
       <c r="D16" s="6" t="inlineStr"/>
     </row>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>339634.09</v>
+        <v>348852.72</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>361896.34</v>
+        <v>377202.7</v>
       </c>
       <c r="D18" s="6" t="inlineStr"/>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>366283.12</v>
+        <v>377202.7</v>
       </c>
       <c r="D19" s="6" t="inlineStr"/>
     </row>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>318507.06</v>
+        <v>328002.35</v>
       </c>
       <c r="D20" s="6" t="inlineStr"/>
     </row>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>191104.24</v>
+        <v>196801.41</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -948,6 +948,12 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -982,35 +988,65 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>Canaleta de concreto 14x19x39</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>9x19x39 - vedação</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Bloco 19x19x39 e canaletas</t>
-        </is>
-      </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Paver 35 MPa</t>
+          <t>9x19x39 - estrutural</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>Canaleta de concreto 9x19x39</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>19x19x39 - vedação</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>19x19x39 - estrutural</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Canaleta de concreto 19x19x39</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Paver 6 cm - 35 MPa</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Paver 8 cm - 50 MPa</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
           <t>Receita do mês (R$)</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Dias de produção</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>% da capacidade mensal</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>Acumulado (R$)</t>
         </is>
@@ -1023,31 +1059,49 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>28587.01</v>
+        <v>21673.81</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>6987.94</v>
+        <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>9632.799999999999</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>35574.95</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I5" s="10" t="n">
-        <v>0.07415793503528434</v>
+        <v>0</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>35574.95</v>
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>31306.61</v>
+      </c>
+      <c r="N5" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O5" s="10" t="n">
+        <v>0.06307895024769879</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>31306.61</v>
       </c>
     </row>
     <row r="6">
@@ -1057,31 +1111,49 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>48597.92</v>
+        <v>36845.47</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>11879.49</v>
+        <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>16375.77</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>60477.41</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I6" s="10" t="n">
-        <v>0.1260684895599834</v>
+        <v>0</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>96052.36</v>
+        <v>0</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>53221.24</v>
+      </c>
+      <c r="N6" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O6" s="10" t="n">
+        <v>0.107234215421088</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>84527.85000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1091,31 +1163,49 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>76232.03</v>
+        <v>57796.82</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>19457.55</v>
+        <v>20203.95</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>18634.5</v>
+        <v>0</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0</v>
+        <v>25687.48</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0</v>
+        <v>1635.56</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>114324.08</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I7" s="10" t="n">
-        <v>0.2383148195305061</v>
+        <v>0</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>210376.44</v>
+        <v>0</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>105323.8</v>
+      </c>
+      <c r="N7" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O7" s="10" t="n">
+        <v>0.2122144335162579</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>189851.66</v>
       </c>
     </row>
     <row r="8">
@@ -1125,31 +1215,49 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>93384.24000000001</v>
+        <v>70801.11</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>33369.69</v>
+        <v>34649.77</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>22827.26</v>
+        <v>4282.47</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>31467.16</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>22480.64</v>
+        <v>2804.98</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>172061.83</v>
-      </c>
-      <c r="H8" s="9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I8" s="10" t="n">
-        <v>0.3586723336424765</v>
+        <v>751.51</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>382438.27</v>
+        <v>0</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>7676.9</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>152433.9</v>
+      </c>
+      <c r="N8" s="9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O8" s="10" t="n">
+        <v>0.307135448630964</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>342285.56</v>
       </c>
     </row>
     <row r="9">
@@ -1159,31 +1267,49 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>111806.98</v>
+        <v>84768.67</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>48514.15</v>
+        <v>50375.17</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>27330.6</v>
+        <v>7178.24</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>37674.97</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>40373.39</v>
+        <v>4077.99</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>228025.11</v>
-      </c>
-      <c r="H9" s="9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="I9" s="10" t="n">
-        <v>0.475330878687127</v>
+        <v>1259.67</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>1345.53</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>6726.1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>610463.38</v>
+        <v>0</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>13787.09</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>207193.44</v>
+      </c>
+      <c r="N9" s="9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="O9" s="10" t="n">
+        <v>0.4174691382613335</v>
+      </c>
+      <c r="P9" s="5" t="n">
+        <v>549478.99</v>
       </c>
     </row>
     <row r="10">
@@ -1193,31 +1319,49 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>118794.92</v>
+        <v>90066.71000000001</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>60642.69</v>
+        <v>62968.97</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>29038.76</v>
+        <v>9261.209999999999</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0</v>
+        <v>40029.65</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>57195.63</v>
+        <v>5097.49</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>265671.99</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="I10" s="10" t="n">
-        <v>0.5538078696513483</v>
+        <v>1625.2</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>2001.48</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>10005.07</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>876135.38</v>
+        <v>944.53</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>19531.72</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>26127.95</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>267659.98</v>
+      </c>
+      <c r="N10" s="9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O10" s="10" t="n">
+        <v>0.5393017512554692</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>817138.97</v>
       </c>
     </row>
     <row r="11">
@@ -1227,31 +1371,49 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>125782.85</v>
+        <v>95364.75999999999</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>64209.91</v>
+        <v>66673.02</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>30746.92</v>
+        <v>11536.46</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>42384.34</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>75700.10000000001</v>
+        <v>5397.34</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>296439.78</v>
-      </c>
-      <c r="H11" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="I11" s="10" t="n">
-        <v>0.6179450063764591</v>
+        <v>2024.46</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>2573.33</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>12863.66</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>1172575.15</v>
+        <v>1400.13</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>25850.8</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>38730.85</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>304799.16</v>
+      </c>
+      <c r="N11" s="9" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="O11" s="10" t="n">
+        <v>0.6141325906170692</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>1121938.13</v>
       </c>
     </row>
     <row r="12">
@@ -1261,31 +1423,49 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>138805.83</v>
+        <v>105238.38</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>70857.89999999999</v>
+        <v>73576.03999999999</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>33930.31</v>
+        <v>12730.89</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>12502.31</v>
+        <v>46772.61</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>83537.74000000001</v>
+        <v>5956.16</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>339634.09</v>
-      </c>
-      <c r="H12" s="9" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="I12" s="10" t="n">
-        <v>0.70798591706938</v>
+        <v>2234.07</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>3340.9</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>16700.59</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>1512209.24</v>
+        <v>1876.19</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>28527.27</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>51899.61</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>348852.72</v>
+      </c>
+      <c r="N12" s="9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="O12" s="10" t="n">
+        <v>0.702895064143464</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>1470790.85</v>
       </c>
     </row>
     <row r="13">
@@ -1295,31 +1475,49 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>146111.4</v>
+        <v>110777.24</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>74587.25999999999</v>
+        <v>77448.46000000001</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>35716.12</v>
+        <v>13400.94</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>17547.1</v>
+        <v>49234.33</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>87934.46000000001</v>
+        <v>6269.64</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>361896.34</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="I13" s="10" t="n">
-        <v>0.7543928095440242</v>
+        <v>2351.65</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>3516.74</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>17579.57</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>1874105.59</v>
+        <v>2323.45</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>30028.71</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>64271.97</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>377202.7</v>
+      </c>
+      <c r="N13" s="9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="O13" s="10" t="n">
+        <v>0.7600167716906291</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>1847993.55</v>
       </c>
     </row>
     <row r="14">
@@ -1329,31 +1527,49 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>146111.4</v>
+        <v>110777.24</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>74587.25999999999</v>
+        <v>77448.46000000001</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>35716.12</v>
+        <v>13400.94</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>21933.88</v>
+        <v>49234.33</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>87934.46000000001</v>
+        <v>6269.64</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>366283.12</v>
-      </c>
-      <c r="H14" s="9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I14" s="10" t="n">
-        <v>0.763537285330806</v>
+        <v>2351.65</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>3516.74</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>17579.57</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>2240388.7</v>
+        <v>2323.45</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>30028.71</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>64271.97</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>377202.7</v>
+      </c>
+      <c r="N14" s="9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="O14" s="10" t="n">
+        <v>0.7600167716906291</v>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>2225196.24</v>
       </c>
     </row>
     <row r="15">
@@ -1363,31 +1579,49 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>127053.39</v>
+        <v>96328.03999999999</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>64858.49</v>
+        <v>67346.49000000001</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>31057.49</v>
+        <v>11652.99</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>19072.94</v>
+        <v>42812.46</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>76464.75</v>
+        <v>5451.86</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>318507.06</v>
-      </c>
-      <c r="H15" s="9" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="I15" s="10" t="n">
-        <v>0.6639454655050485</v>
+        <v>2044.91</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>3058.03</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>15286.58</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>2558895.76</v>
+        <v>2020.39</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>26111.92</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>55888.67</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>328002.35</v>
+      </c>
+      <c r="N15" s="9" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="O15" s="10" t="n">
+        <v>0.6608841492961993</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>2553198.59</v>
       </c>
     </row>
     <row r="16">
@@ -1397,30 +1631,48 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>76232.03</v>
+        <v>57796.82</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>38915.09</v>
+        <v>40407.89</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>18634.5</v>
+        <v>6991.79</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>11443.76</v>
+        <v>25687.48</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>45878.85</v>
+        <v>3271.12</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>191104.24</v>
-      </c>
-      <c r="H16" s="9" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="I16" s="10" t="n">
-        <v>0.3983672793030292</v>
+        <v>1226.95</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1834.82</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>9171.950000000001</v>
       </c>
       <c r="J16" s="5" t="n">
+        <v>1212.24</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>15667.15</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>33533.2</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>196801.41</v>
+      </c>
+      <c r="N16" s="9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O16" s="10" t="n">
+        <v>0.3965304895777196</v>
+      </c>
+      <c r="P16" s="5" t="n">
         <v>2750000</v>
       </c>
     </row>
@@ -1450,12 +1702,36 @@
         <f>SUM(F5:F16)</f>
         <v/>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="5">
         <f>SUM(G5:G16)</f>
         <v/>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="5">
         <f>SUM(H5:H16)</f>
+        <v/>
+      </c>
+      <c r="I17" s="5">
+        <f>SUM(I5:I16)</f>
+        <v/>
+      </c>
+      <c r="J17" s="5">
+        <f>SUM(J5:J16)</f>
+        <v/>
+      </c>
+      <c r="K17" s="5">
+        <f>SUM(K5:K16)</f>
+        <v/>
+      </c>
+      <c r="L17" s="5">
+        <f>SUM(L5:L16)</f>
+        <v/>
+      </c>
+      <c r="M17" s="8">
+        <f>SUM(M5:M16)</f>
+        <v/>
+      </c>
+      <c r="N17" s="9">
+        <f>SUM(N5:N16)</f>
         <v/>
       </c>
     </row>
@@ -1473,7 +1749,13 @@
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
       <c r="I19" s="12" t="n"/>
-      <c r="J19" s="13" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="12" t="n"/>
+      <c r="N19" s="12" t="n"/>
+      <c r="O19" s="12" t="n"/>
+      <c r="P19" s="13" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1493,35 +1775,65 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
+          <t>Canaleta de concreto 14x19x3</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Bloco de concreto 9x19x39 - </t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Bloco 19x19x39 e canaletas</t>
-        </is>
-      </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Piso intertravado (paver) 35</t>
+          <t xml:space="preserve">Bloco de concreto 9x19x39 - </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
+          <t>Canaleta de concreto 9x19x39</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Bloco de concreto 19x19x39 -</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Bloco de concreto 19x19x39 -</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Canaleta de concreto 19x19x3</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Piso intertravado (paver) 6 </t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Piso intertravado (paver) 8 </t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="N20" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="O20" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="P20" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1534,18 +1846,36 @@
         </is>
       </c>
       <c r="B21" s="14" t="n">
-        <v>8663</v>
+        <v>6568</v>
       </c>
       <c r="C21" s="14" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>2496</v>
+        <v>0</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>0</v>
+        <v>3440</v>
       </c>
       <c r="F21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1556,18 +1886,36 @@
         </is>
       </c>
       <c r="B22" s="14" t="n">
-        <v>14727</v>
+        <v>11165</v>
       </c>
       <c r="C22" s="14" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>4243</v>
+        <v>0</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>0</v>
+        <v>5848</v>
       </c>
       <c r="F22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1578,18 +1926,36 @@
         </is>
       </c>
       <c r="B23" s="14" t="n">
-        <v>23101</v>
+        <v>17514</v>
       </c>
       <c r="C23" s="14" t="n">
-        <v>4324</v>
+        <v>4490</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>6655</v>
+        <v>0</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>0</v>
+        <v>9174</v>
       </c>
       <c r="F23" s="14" t="n">
+        <v>481</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1600,19 +1966,37 @@
         </is>
       </c>
       <c r="B24" s="14" t="n">
-        <v>28298</v>
+        <v>21455</v>
       </c>
       <c r="C24" s="14" t="n">
-        <v>7415</v>
+        <v>7700</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>8153</v>
+        <v>856</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>0</v>
+        <v>11238</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>394</v>
+        <v>825</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>198</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="14" t="n">
+        <v>135</v>
+      </c>
+      <c r="L24" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1622,19 +2006,37 @@
         </is>
       </c>
       <c r="B25" s="14" t="n">
-        <v>33881</v>
+        <v>25687</v>
       </c>
       <c r="C25" s="14" t="n">
-        <v>10781</v>
+        <v>11194</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>9761</v>
+        <v>1436</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>0</v>
+        <v>13455</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>708</v>
+        <v>1199</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>331</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>306</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>1223</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="14" t="n">
+        <v>242</v>
+      </c>
+      <c r="L25" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1644,19 +2046,37 @@
         </is>
       </c>
       <c r="B26" s="14" t="n">
-        <v>35998</v>
+        <v>27293</v>
       </c>
       <c r="C26" s="14" t="n">
-        <v>13476</v>
+        <v>13993</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>10371</v>
+        <v>1852</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>0</v>
+        <v>14296</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>1003</v>
+        <v>1499</v>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>428</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>455</v>
+      </c>
+      <c r="I26" s="14" t="n">
+        <v>1819</v>
+      </c>
+      <c r="J26" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="K26" s="14" t="n">
+        <v>343</v>
+      </c>
+      <c r="L26" s="14" t="n">
+        <v>335</v>
       </c>
     </row>
     <row r="27">
@@ -1666,19 +2086,37 @@
         </is>
       </c>
       <c r="B27" s="14" t="n">
-        <v>38116</v>
+        <v>28898</v>
       </c>
       <c r="C27" s="14" t="n">
-        <v>14269</v>
+        <v>14816</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>10981</v>
+        <v>2307</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>0</v>
+        <v>15137</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>1328</v>
+        <v>1587</v>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>533</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>585</v>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>2339</v>
+      </c>
+      <c r="J27" s="14" t="n">
+        <v>222</v>
+      </c>
+      <c r="K27" s="14" t="n">
+        <v>454</v>
+      </c>
+      <c r="L27" s="14" t="n">
+        <v>497</v>
       </c>
     </row>
     <row r="28">
@@ -1688,19 +2126,37 @@
         </is>
       </c>
       <c r="B28" s="14" t="n">
-        <v>42062</v>
+        <v>31890</v>
       </c>
       <c r="C28" s="14" t="n">
-        <v>15746</v>
+        <v>16350</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>12118</v>
+        <v>2546</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>2273</v>
+        <v>16705</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1466</v>
+        <v>1752</v>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>588</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>759</v>
+      </c>
+      <c r="I28" s="14" t="n">
+        <v>3036</v>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>298</v>
+      </c>
+      <c r="K28" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="L28" s="14" t="n">
+        <v>665</v>
       </c>
     </row>
     <row r="29">
@@ -1710,19 +2166,37 @@
         </is>
       </c>
       <c r="B29" s="14" t="n">
-        <v>44276</v>
+        <v>33569</v>
       </c>
       <c r="C29" s="14" t="n">
-        <v>16575</v>
+        <v>17211</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>12756</v>
+        <v>2680</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>3190</v>
+        <v>17584</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>1543</v>
+        <v>1844</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>619</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>799</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>3196</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>369</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>527</v>
+      </c>
+      <c r="L29" s="14" t="n">
+        <v>824</v>
       </c>
     </row>
     <row r="30">
@@ -1732,19 +2206,37 @@
         </is>
       </c>
       <c r="B30" s="14" t="n">
-        <v>44276</v>
+        <v>33569</v>
       </c>
       <c r="C30" s="14" t="n">
-        <v>16575</v>
+        <v>17211</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>12756</v>
+        <v>2680</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>3988</v>
+        <v>17584</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>1543</v>
+        <v>1844</v>
+      </c>
+      <c r="G30" s="14" t="n">
+        <v>619</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>799</v>
+      </c>
+      <c r="I30" s="14" t="n">
+        <v>3196</v>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>369</v>
+      </c>
+      <c r="K30" s="14" t="n">
+        <v>527</v>
+      </c>
+      <c r="L30" s="14" t="n">
+        <v>824</v>
       </c>
     </row>
     <row r="31">
@@ -1754,19 +2246,37 @@
         </is>
       </c>
       <c r="B31" s="14" t="n">
-        <v>38501</v>
+        <v>29190</v>
       </c>
       <c r="C31" s="14" t="n">
-        <v>14413</v>
+        <v>14966</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>11092</v>
+        <v>2331</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>3468</v>
+        <v>15290</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>1341</v>
+        <v>1603</v>
+      </c>
+      <c r="G31" s="14" t="n">
+        <v>538</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>695</v>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>2779</v>
+      </c>
+      <c r="J31" s="14" t="n">
+        <v>321</v>
+      </c>
+      <c r="K31" s="14" t="n">
+        <v>458</v>
+      </c>
+      <c r="L31" s="14" t="n">
+        <v>717</v>
       </c>
     </row>
     <row r="32">
@@ -1776,19 +2286,37 @@
         </is>
       </c>
       <c r="B32" s="14" t="n">
-        <v>23101</v>
+        <v>17514</v>
       </c>
       <c r="C32" s="14" t="n">
-        <v>8648</v>
+        <v>8980</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>6655</v>
+        <v>1398</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>2081</v>
+        <v>9174</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>805</v>
+        <v>962</v>
+      </c>
+      <c r="G32" s="14" t="n">
+        <v>323</v>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>417</v>
+      </c>
+      <c r="I32" s="14" t="n">
+        <v>1668</v>
+      </c>
+      <c r="J32" s="14" t="n">
+        <v>192</v>
+      </c>
+      <c r="K32" s="14" t="n">
+        <v>275</v>
+      </c>
+      <c r="L32" s="14" t="n">
+        <v>430</v>
       </c>
     </row>
     <row r="33">
@@ -1817,10 +2345,34 @@
         <f>SUM(F21:F32)</f>
         <v/>
       </c>
+      <c r="G33" s="14">
+        <f>SUM(G21:G32)</f>
+        <v/>
+      </c>
+      <c r="H33" s="14">
+        <f>SUM(H21:H32)</f>
+        <v/>
+      </c>
+      <c r="I33" s="14">
+        <f>SUM(I21:I32)</f>
+        <v/>
+      </c>
+      <c r="J33" s="14">
+        <f>SUM(J21:J32)</f>
+        <v/>
+      </c>
+      <c r="K33" s="14">
+        <f>SUM(K21:K32)</f>
+        <v/>
+      </c>
+      <c r="L33" s="14">
+        <f>SUM(L21:L32)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A19:P19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1832,7 +2384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1845,6 +2397,12 @@
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1884,32 +2442,62 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>Canaleta de concreto 14x19</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Bloco de concreto 9x19x39 </t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Bloco 19x19x39 e canaletas</t>
-        </is>
-      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bloco de concreto 9x19x39 </t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Canaleta de concreto 9x19x</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Bloco de concreto 19x19x39</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Bloco de concreto 19x19x39</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Canaleta de concreto 19x19</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Piso intertravado (paver) </t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Piso intertravado (paver) </t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Receita total (R$)</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>Dias de produção</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>% capac. efetiva (210 d)</t>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>% capac. efetiva (207 d)</t>
         </is>
       </c>
     </row>
@@ -1921,28 +2509,46 @@
         <v>2027</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1237500</v>
+        <v>938235.08</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>550000</v>
+        <v>571098.23</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>302500</v>
+        <v>90435.92999999999</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>82500</v>
+        <v>416993.37</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>577500</v>
+        <v>46231.76</v>
       </c>
       <c r="H5" s="5" t="n">
+        <v>15870.06</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>21187.58</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>105913.1</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>12100.4</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>197210.27</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>334724.22</v>
+      </c>
+      <c r="N5" s="5" t="n">
         <v>2750000</v>
       </c>
-      <c r="I5" s="9" t="n">
-        <v>103.1</v>
-      </c>
-      <c r="J5" s="10" t="n">
-        <v>0.4907350850169112</v>
+      <c r="O5" s="9" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="P5" s="10" t="n">
+        <v>0.4717886866871852</v>
       </c>
     </row>
     <row r="6">
@@ -1953,28 +2559,46 @@
         <v>2028</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1540000</v>
+        <v>1194671.74</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>885500</v>
+        <v>793659.4300000001</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>385000</v>
+        <v>133220.29</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>134750</v>
+        <v>530965.22</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>904750</v>
+        <v>64248.62</v>
       </c>
       <c r="H6" s="5" t="n">
+        <v>23378.04</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>33713.23</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>168526.7</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>21343.83</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>295854.4</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>590418.5</v>
+      </c>
+      <c r="N6" s="5" t="n">
         <v>3850000</v>
       </c>
-      <c r="I6" s="9" t="n">
-        <v>142.2</v>
-      </c>
-      <c r="J6" s="10" t="n">
-        <v>0.6769892816639663</v>
+      <c r="O6" s="9" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="P6" s="10" t="n">
+        <v>0.6513621143648169</v>
       </c>
     </row>
     <row r="7">
@@ -1985,28 +2609,46 @@
         <v>2029</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1724760</v>
+        <v>1407025.38</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1245660</v>
+        <v>983703.42</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>431190</v>
+        <v>170210.57</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>191640</v>
+        <v>625344.61</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1197750</v>
-      </c>
-      <c r="H7" s="15" t="n">
+        <v>79633.13</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>29869.24</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>44667.47</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>223285.06</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>29511.1</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>381406.42</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>816343.58</v>
+      </c>
+      <c r="N7" s="15" t="n">
         <v>4791000</v>
       </c>
-      <c r="I7" s="9" t="n">
-        <v>174.8</v>
-      </c>
-      <c r="J7" s="10" t="n">
-        <v>0.8322585604099136</v>
+      <c r="O7" s="9" t="n">
+        <v>166.5</v>
+      </c>
+      <c r="P7" s="10" t="n">
+        <v>0.8044393554213264</v>
       </c>
     </row>
     <row r="8">
@@ -2017,28 +2659,46 @@
         <v>2030</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1724760</v>
+        <v>1407025.38</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1245660</v>
+        <v>983703.42</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>431190</v>
+        <v>170210.57</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>191640</v>
+        <v>625344.61</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1197750</v>
-      </c>
-      <c r="H8" s="15" t="n">
+        <v>79633.13</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>29869.24</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>44667.47</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>223285.06</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>29511.1</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>381406.42</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>816343.58</v>
+      </c>
+      <c r="N8" s="15" t="n">
         <v>4791000</v>
       </c>
-      <c r="I8" s="9" t="n">
-        <v>174.8</v>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>0.8322585604099136</v>
+      <c r="O8" s="9" t="n">
+        <v>166.5</v>
+      </c>
+      <c r="P8" s="10" t="n">
+        <v>0.8044393554213264</v>
       </c>
     </row>
     <row r="9">
@@ -2049,28 +2709,46 @@
         <v>2031</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1724760</v>
+        <v>1407025.38</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1245660</v>
+        <v>983703.42</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>431190</v>
+        <v>170210.57</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>191640</v>
+        <v>625344.61</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1197750</v>
-      </c>
-      <c r="H9" s="15" t="n">
+        <v>79633.13</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>29869.24</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>44667.47</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>223285.06</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>29511.1</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>381406.42</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>816343.58</v>
+      </c>
+      <c r="N9" s="15" t="n">
         <v>4791000</v>
       </c>
-      <c r="I9" s="9" t="n">
-        <v>174.8</v>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>0.8322585604099136</v>
+      <c r="O9" s="9" t="n">
+        <v>166.5</v>
+      </c>
+      <c r="P9" s="10" t="n">
+        <v>0.8044393554213264</v>
       </c>
     </row>
     <row r="10">
@@ -2081,28 +2759,46 @@
         <v>2032</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1724760</v>
+        <v>1407025.38</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1245660</v>
+        <v>983703.42</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>431190</v>
+        <v>170210.57</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>191640</v>
+        <v>625344.61</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1197750</v>
-      </c>
-      <c r="H10" s="15" t="n">
+        <v>79633.13</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>29869.24</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>44667.47</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>223285.06</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>29511.1</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>381406.42</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>816343.58</v>
+      </c>
+      <c r="N10" s="15" t="n">
         <v>4791000</v>
       </c>
-      <c r="I10" s="9" t="n">
-        <v>174.8</v>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v>0.8322585604099136</v>
+      <c r="O10" s="9" t="n">
+        <v>166.5</v>
+      </c>
+      <c r="P10" s="10" t="n">
+        <v>0.8044393554213264</v>
       </c>
     </row>
     <row r="11">
@@ -2113,28 +2809,46 @@
         <v>2033</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1724760</v>
+        <v>1407025.38</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1245660</v>
+        <v>983703.42</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>431190</v>
+        <v>170210.57</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>191640</v>
+        <v>625344.61</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1197750</v>
-      </c>
-      <c r="H11" s="15" t="n">
+        <v>79633.13</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>29869.24</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>44667.47</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>223285.06</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>29511.1</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>381406.42</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>816343.58</v>
+      </c>
+      <c r="N11" s="15" t="n">
         <v>4791000</v>
       </c>
-      <c r="I11" s="9" t="n">
-        <v>174.8</v>
-      </c>
-      <c r="J11" s="10" t="n">
-        <v>0.8322585604099136</v>
+      <c r="O11" s="9" t="n">
+        <v>166.5</v>
+      </c>
+      <c r="P11" s="10" t="n">
+        <v>0.8044393554213264</v>
       </c>
     </row>
     <row r="12">
@@ -2145,28 +2859,46 @@
         <v>2034</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>1724760</v>
+        <v>1407025.38</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1245660</v>
+        <v>983703.42</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>431190</v>
+        <v>170210.57</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>191640</v>
+        <v>625344.61</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1197750</v>
-      </c>
-      <c r="H12" s="15" t="n">
+        <v>79633.13</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>29869.24</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>44667.47</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>223285.06</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>29511.1</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>381406.42</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>816343.58</v>
+      </c>
+      <c r="N12" s="15" t="n">
         <v>4791000</v>
       </c>
-      <c r="I12" s="9" t="n">
-        <v>174.8</v>
-      </c>
-      <c r="J12" s="10" t="n">
-        <v>0.8322585604099136</v>
+      <c r="O12" s="9" t="n">
+        <v>166.5</v>
+      </c>
+      <c r="P12" s="10" t="n">
+        <v>0.8044393554213264</v>
       </c>
     </row>
     <row r="13">
@@ -2177,28 +2909,46 @@
         <v>2035</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1724760</v>
+        <v>1407025.38</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1245660</v>
+        <v>983703.42</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>431190</v>
+        <v>170210.57</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>191640</v>
+        <v>625344.61</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1197750</v>
-      </c>
-      <c r="H13" s="15" t="n">
+        <v>79633.13</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>29869.24</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>44667.47</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>223285.06</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>29511.1</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>381406.42</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>816343.58</v>
+      </c>
+      <c r="N13" s="15" t="n">
         <v>4791000</v>
       </c>
-      <c r="I13" s="9" t="n">
-        <v>174.8</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>0.8322585604099136</v>
+      <c r="O13" s="9" t="n">
+        <v>166.5</v>
+      </c>
+      <c r="P13" s="10" t="n">
+        <v>0.8044393554213264</v>
       </c>
     </row>
     <row r="14">
@@ -2209,28 +2959,46 @@
         <v>2036</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>1724760</v>
+        <v>1407025.38</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1245660</v>
+        <v>983703.42</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>431190</v>
+        <v>170210.57</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>191640</v>
+        <v>625344.61</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1197750</v>
-      </c>
-      <c r="H14" s="15" t="n">
+        <v>79633.13</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>29869.24</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>44667.47</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>223285.06</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>29511.1</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>381406.42</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>816343.58</v>
+      </c>
+      <c r="N14" s="15" t="n">
         <v>4791000</v>
       </c>
-      <c r="I14" s="9" t="n">
-        <v>174.8</v>
-      </c>
-      <c r="J14" s="10" t="n">
-        <v>0.8322585604099136</v>
+      <c r="O14" s="9" t="n">
+        <v>166.5</v>
+      </c>
+      <c r="P14" s="10" t="n">
+        <v>0.8044393554213264</v>
       </c>
     </row>
     <row r="15">
@@ -2241,28 +3009,46 @@
         <v>2037</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1724760</v>
+        <v>1407025.38</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1245660</v>
+        <v>983703.42</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>431190</v>
+        <v>170210.57</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>191640</v>
+        <v>625344.61</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1197750</v>
-      </c>
-      <c r="H15" s="15" t="n">
+        <v>79633.13</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>29869.24</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>44667.47</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>223285.06</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>29511.1</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>381406.42</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>816343.58</v>
+      </c>
+      <c r="N15" s="15" t="n">
         <v>4791000</v>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>174.8</v>
-      </c>
-      <c r="J15" s="10" t="n">
-        <v>0.8322585604099136</v>
+      <c r="O15" s="9" t="n">
+        <v>166.5</v>
+      </c>
+      <c r="P15" s="10" t="n">
+        <v>0.8044393554213264</v>
       </c>
     </row>
     <row r="16">
@@ -2273,28 +3059,46 @@
         <v>2038</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>1724760</v>
+        <v>1407025.38</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1245660</v>
+        <v>983703.42</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>431190</v>
+        <v>170210.57</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>191640</v>
+        <v>625344.61</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>1197750</v>
-      </c>
-      <c r="H16" s="15" t="n">
+        <v>79633.13</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>29869.24</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>44667.47</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>223285.06</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>29511.1</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>381406.42</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>816343.58</v>
+      </c>
+      <c r="N16" s="15" t="n">
         <v>4791000</v>
       </c>
-      <c r="I16" s="9" t="n">
-        <v>174.8</v>
-      </c>
-      <c r="J16" s="10" t="n">
-        <v>0.8322585604099136</v>
+      <c r="O16" s="9" t="n">
+        <v>166.5</v>
+      </c>
+      <c r="P16" s="10" t="n">
+        <v>0.8044393554213264</v>
       </c>
     </row>
     <row r="17">
@@ -2306,27 +3110,57 @@
       <c r="B17" s="13" t="n"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>45% / 40.0% / 36%</t>
+          <t>34.1% / 31.0% / 29.4%</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>20% / 23.0% / 26%</t>
+          <t>20.8% / 20.6% / 20.5%</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>11% / 10.0% / 9%</t>
+          <t>3.3% / 3.5% / 3.6%</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>3% / 3.5% / 4%</t>
+          <t>15.2% / 13.8% / 13.1%</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>21% / 23.5% / 25%</t>
+          <t>1.7% / 1.7% / 1.7%</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>0.6% / 0.6% / 0.6%</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>0.8% / 0.9% / 0.9%</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>3.9% / 4.4% / 4.7%</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>0.4% / 0.6% / 0.6%</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>7.2% / 7.7% / 8.0%</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>12.2% / 15.3% / 17.0%</t>
         </is>
       </c>
     </row>
@@ -2344,7 +3178,13 @@
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
       <c r="I19" s="12" t="n"/>
-      <c r="J19" s="13" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="12" t="n"/>
+      <c r="N19" s="12" t="n"/>
+      <c r="O19" s="12" t="n"/>
+      <c r="P19" s="13" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -2503,7 +3343,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A19:P19"/>
     <mergeCell ref="A17:B17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3003,12 +3843,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>103.1 de 210</t>
+          <t>97.7 de 207</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>✓ 49% da capacidade efetiva</t>
+          <t>✓ 47% da capacidade efetiva</t>
         </is>
       </c>
     </row>
@@ -3020,12 +3860,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>142.2 de 210</t>
+          <t>134.8 de 207</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>✓ 68%</t>
+          <t>✓ 65%</t>
         </is>
       </c>
     </row>
@@ -3037,12 +3877,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>174.8 de 210</t>
+          <t>166.5 de 207</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>✓ 83% (§3.7)</t>
+          <t>✓ 80% (§3.7)</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3894,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>76.4% da capacidade mensal</t>
+          <t>76.0% da capacidade mensal</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -3071,12 +3911,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>R$ 479.719</t>
+          <t>R$ 496.308</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>210 dias ÷ 12 × R$/dia do mix</t>
+          <t>207 dias ÷ 12 × R$/dia do mix</t>
         </is>
       </c>
     </row>

--- a/estudo-mercado-gtk/dossie-bnb/previsao-faturamento.xlsx
+++ b/estudo-mercado-gtk/dossie-bnb/previsao-faturamento.xlsx
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>31306.61</v>
+        <v>31452.59</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>53221.24</v>
+        <v>53469.4</v>
       </c>
       <c r="D11" s="6" t="inlineStr"/>
     </row>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>105323.8</v>
+        <v>105506.7</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>152433.9</v>
+        <v>153037.92</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>207193.44</v>
+        <v>208605.48</v>
       </c>
       <c r="D14" s="6" t="inlineStr"/>
     </row>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>267659.98</v>
+        <v>267968.87</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>304799.16</v>
+        <v>305003.32</v>
       </c>
       <c r="D16" s="6" t="inlineStr"/>
     </row>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>348852.72</v>
+        <v>348640.78</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>377202.7</v>
+        <v>376349.28</v>
       </c>
       <c r="D18" s="6" t="inlineStr"/>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>377202.7</v>
+        <v>376349.28</v>
       </c>
       <c r="D19" s="6" t="inlineStr"/>
     </row>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>328002.35</v>
+        <v>327260.24</v>
       </c>
       <c r="D20" s="6" t="inlineStr"/>
     </row>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>196801.41</v>
+        <v>196356.15</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>21673.81</v>
+        <v>22150.27</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>0</v>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>9632.799999999999</v>
+        <v>9302.309999999999</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -1092,16 +1092,16 @@
         <v>0</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>31306.61</v>
+        <v>31452.59</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="O5" s="10" t="n">
-        <v>0.06307895024769879</v>
+        <v>0.06584215689850713</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>31306.61</v>
+        <v>31452.59</v>
       </c>
     </row>
     <row r="6">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>36845.47</v>
+        <v>37655.46</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>0</v>
@@ -1120,7 +1120,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>16375.77</v>
+        <v>15813.93</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -1144,16 +1144,16 @@
         <v>0</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>53221.24</v>
+        <v>53469.4</v>
       </c>
       <c r="N6" s="9" t="n">
         <v>2.1</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>0.107234215421088</v>
+        <v>0.1119316667274621</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>84527.85000000001</v>
+        <v>84921.98</v>
       </c>
     </row>
     <row r="7">
@@ -1163,19 +1163,19 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>57796.82</v>
+        <v>59067.39</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>20203.95</v>
+        <v>20220.03</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>25687.48</v>
+        <v>24806.17</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1635.56</v>
+        <v>1413.12</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0</v>
@@ -1196,16 +1196,16 @@
         <v>0</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>105323.8</v>
+        <v>105506.7</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O7" s="10" t="n">
-        <v>0.2122144335162579</v>
+        <v>0.2208654326700041</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>189851.66</v>
+        <v>190428.68</v>
       </c>
     </row>
     <row r="8">
@@ -1215,22 +1215,22 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>70801.11</v>
+        <v>72357.55</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>34649.77</v>
+        <v>34677.34</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>4282.47</v>
+        <v>3948.53</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>31467.16</v>
+        <v>30387.56</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>2804.98</v>
+        <v>2423.49</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>751.51</v>
+        <v>602.12</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0</v>
@@ -1242,22 +1242,22 @@
         <v>0</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>7676.9</v>
+        <v>8641.32</v>
       </c>
       <c r="L8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>152433.9</v>
+        <v>153037.92</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O8" s="10" t="n">
-        <v>0.307135448630964</v>
+        <v>0.3203662436043561</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>342285.56</v>
+        <v>343466.6</v>
       </c>
     </row>
     <row r="9">
@@ -1267,49 +1267,49 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>84768.67</v>
+        <v>86632.17</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>50375.17</v>
+        <v>50415.26</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>7178.24</v>
+        <v>6618.48</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>37674.97</v>
+        <v>36382.38</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>4077.99</v>
+        <v>3523.37</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1259.67</v>
+        <v>1009.27</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>1345.53</v>
+        <v>1280.9</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>6726.1</v>
+        <v>7224.53</v>
       </c>
       <c r="J9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>13787.09</v>
+        <v>15519.11</v>
       </c>
       <c r="L9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>207193.44</v>
+        <v>208605.48</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O9" s="10" t="n">
-        <v>0.4174691382613335</v>
+        <v>0.4366901667944827</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>549478.99</v>
+        <v>552072.08</v>
       </c>
     </row>
     <row r="10">
@@ -1319,49 +1319,49 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>90066.71000000001</v>
+        <v>92046.67999999999</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>62968.97</v>
+        <v>63019.08</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>9261.209999999999</v>
+        <v>8539.030000000001</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>40029.65</v>
+        <v>38656.28</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>5097.49</v>
+        <v>4404.21</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1625.2</v>
+        <v>1302.13</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>2001.48</v>
+        <v>1905.34</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>10005.07</v>
+        <v>10746.49</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>944.53</v>
+        <v>856.55</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>19531.72</v>
+        <v>21985.4</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>26127.95</v>
+        <v>24507.67</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>267659.98</v>
+        <v>267968.87</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O10" s="10" t="n">
-        <v>0.5393017512554692</v>
+        <v>0.5609601950759683</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>817138.97</v>
+        <v>820040.95</v>
       </c>
     </row>
     <row r="11">
@@ -1371,49 +1371,49 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>95364.75999999999</v>
+        <v>97461.19</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>66673.02</v>
+        <v>66726.09</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>11536.46</v>
+        <v>10636.85</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>42384.34</v>
+        <v>40930.18</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>5397.34</v>
+        <v>4663.28</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>2024.46</v>
+        <v>1622.04</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>2573.33</v>
+        <v>2449.72</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>12863.66</v>
+        <v>13816.92</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>1400.13</v>
+        <v>1269.72</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>25850.8</v>
+        <v>29098.33</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>38730.85</v>
+        <v>36329.01</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>304799.16</v>
+        <v>305003.32</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="O11" s="10" t="n">
-        <v>0.6141325906170692</v>
+        <v>0.6384873040118203</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>1121938.13</v>
+        <v>1125044.27</v>
       </c>
     </row>
     <row r="12">
@@ -1423,49 +1423,49 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>105238.38</v>
+        <v>107551.87</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>73576.03999999999</v>
+        <v>73634.59</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>12730.89</v>
+        <v>11738.14</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>46772.61</v>
+        <v>45167.9</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>5956.16</v>
+        <v>5146.1</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>2234.07</v>
+        <v>1789.97</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>3340.9</v>
+        <v>3180.42</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>16700.59</v>
+        <v>17938.18</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>1876.19</v>
+        <v>1701.43</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>28527.27</v>
+        <v>32111.03</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>51899.61</v>
+        <v>48681.14</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>348852.72</v>
+        <v>348640.78</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="O12" s="10" t="n">
-        <v>0.702895064143464</v>
+        <v>0.7298370066666164</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>1470790.85</v>
+        <v>1473685.05</v>
       </c>
     </row>
     <row r="13">
@@ -1475,49 +1475,49 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>110777.24</v>
+        <v>113212.5</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>77448.46000000001</v>
+        <v>77510.10000000001</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>13400.94</v>
+        <v>12355.94</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>49234.33</v>
+        <v>47545.16</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>6269.64</v>
+        <v>5416.94</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>2351.65</v>
+        <v>1884.18</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>3516.74</v>
+        <v>3347.81</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>17579.57</v>
+        <v>18882.3</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>2323.45</v>
+        <v>2107.03</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>30028.71</v>
+        <v>33801.08</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>64271.97</v>
+        <v>60286.24</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>377202.7</v>
+        <v>376349.28</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>13.1</v>
+        <v>13.6</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>0.7600167716906291</v>
+        <v>0.7878413867196007</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>1847993.55</v>
+        <v>1850034.33</v>
       </c>
     </row>
     <row r="14">
@@ -1527,49 +1527,49 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>110777.24</v>
+        <v>113212.5</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>77448.46000000001</v>
+        <v>77510.10000000001</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>13400.94</v>
+        <v>12355.94</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>49234.33</v>
+        <v>47545.16</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>6269.64</v>
+        <v>5416.94</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>2351.65</v>
+        <v>1884.18</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>3516.74</v>
+        <v>3347.81</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>17579.57</v>
+        <v>18882.3</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>2323.45</v>
+        <v>2107.03</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>30028.71</v>
+        <v>33801.08</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>64271.97</v>
+        <v>60286.24</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>377202.7</v>
+        <v>376349.28</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>13.1</v>
+        <v>13.6</v>
       </c>
       <c r="O14" s="10" t="n">
-        <v>0.7600167716906291</v>
+        <v>0.7878413867196007</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>2225196.24</v>
+        <v>2226383.61</v>
       </c>
     </row>
     <row r="15">
@@ -1579,49 +1579,49 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>96328.03999999999</v>
+        <v>98445.64999999999</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>67346.49000000001</v>
+        <v>67400.09</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>11652.99</v>
+        <v>10744.29</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>42812.46</v>
+        <v>41343.62</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>5451.86</v>
+        <v>4710.39</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>2044.91</v>
+        <v>1638.42</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>3058.03</v>
+        <v>2911.14</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>15286.58</v>
+        <v>16419.39</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>2020.39</v>
+        <v>1832.2</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>26111.92</v>
+        <v>29392.25</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>55888.67</v>
+        <v>52422.81</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>328002.35</v>
+        <v>327260.24</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="O15" s="10" t="n">
-        <v>0.6608841492961993</v>
+        <v>0.6850794667126963</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>2553198.59</v>
+        <v>2553643.85</v>
       </c>
     </row>
     <row r="16">
@@ -1631,46 +1631,46 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>57796.82</v>
+        <v>59067.39</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>40407.89</v>
+        <v>40440.05</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>6991.79</v>
+        <v>6446.58</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>25687.48</v>
+        <v>24806.17</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>3271.12</v>
+        <v>2826.23</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>1226.95</v>
+        <v>983.05</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>1834.82</v>
+        <v>1746.68</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>9171.950000000001</v>
+        <v>9851.629999999999</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>1212.24</v>
+        <v>1099.32</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>15667.15</v>
+        <v>17635.35</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>33533.2</v>
+        <v>31453.69</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>196801.41</v>
+        <v>196356.15</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="O16" s="10" t="n">
-        <v>0.3965304895777196</v>
+        <v>0.4110476800276178</v>
       </c>
       <c r="P16" s="5" t="n">
         <v>2750000</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B21" s="14" t="n">
-        <v>6568</v>
+        <v>6458</v>
       </c>
       <c r="C21" s="14" t="n">
         <v>0</v>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>3440</v>
+        <v>3383</v>
       </c>
       <c r="F21" s="14" t="n">
         <v>0</v>
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="B22" s="14" t="n">
-        <v>11165</v>
+        <v>10978</v>
       </c>
       <c r="C22" s="14" t="n">
         <v>0</v>
@@ -1895,7 +1895,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>5848</v>
+        <v>5751</v>
       </c>
       <c r="F22" s="14" t="n">
         <v>0</v>
@@ -1926,19 +1926,19 @@
         </is>
       </c>
       <c r="B23" s="14" t="n">
-        <v>17514</v>
+        <v>17221</v>
       </c>
       <c r="C23" s="14" t="n">
-        <v>4490</v>
+        <v>4849</v>
       </c>
       <c r="D23" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>9174</v>
+        <v>9020</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>481</v>
+        <v>520</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>0</v>
@@ -1966,22 +1966,22 @@
         </is>
       </c>
       <c r="B24" s="14" t="n">
-        <v>21455</v>
+        <v>21095</v>
       </c>
       <c r="C24" s="14" t="n">
-        <v>7700</v>
+        <v>8316</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>856</v>
+        <v>895</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>11238</v>
+        <v>11050</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>825</v>
+        <v>891</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="H24" s="14" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L24" s="14" t="n">
         <v>0</v>
@@ -2006,34 +2006,34 @@
         </is>
       </c>
       <c r="B25" s="14" t="n">
-        <v>25687</v>
+        <v>25257</v>
       </c>
       <c r="C25" s="14" t="n">
-        <v>11194</v>
+        <v>12090</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>1436</v>
+        <v>1501</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>13455</v>
+        <v>13230</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>1199</v>
+        <v>1295</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>1223</v>
+        <v>1321</v>
       </c>
       <c r="J25" s="14" t="n">
         <v>0</v>
       </c>
       <c r="K25" s="14" t="n">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="L25" s="14" t="n">
         <v>0</v>
@@ -2046,37 +2046,37 @@
         </is>
       </c>
       <c r="B26" s="14" t="n">
-        <v>27293</v>
+        <v>26836</v>
       </c>
       <c r="C26" s="14" t="n">
-        <v>13993</v>
+        <v>15112</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>1852</v>
+        <v>1936</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>14296</v>
+        <v>14057</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>1499</v>
+        <v>1619</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="H26" s="14" t="n">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>1819</v>
+        <v>1965</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>343</v>
+        <v>381</v>
       </c>
       <c r="L26" s="14" t="n">
-        <v>335</v>
+        <v>372</v>
       </c>
     </row>
     <row r="27">
@@ -2086,37 +2086,37 @@
         </is>
       </c>
       <c r="B27" s="14" t="n">
-        <v>28898</v>
+        <v>28414</v>
       </c>
       <c r="C27" s="14" t="n">
-        <v>14816</v>
+        <v>16001</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>2307</v>
+        <v>2412</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>15137</v>
+        <v>14884</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>1587</v>
+        <v>1714</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="H27" s="14" t="n">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>2339</v>
+        <v>2526</v>
       </c>
       <c r="J27" s="14" t="n">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="K27" s="14" t="n">
-        <v>454</v>
+        <v>504</v>
       </c>
       <c r="L27" s="14" t="n">
-        <v>497</v>
+        <v>552</v>
       </c>
     </row>
     <row r="28">
@@ -2126,37 +2126,37 @@
         </is>
       </c>
       <c r="B28" s="14" t="n">
-        <v>31890</v>
+        <v>31356</v>
       </c>
       <c r="C28" s="14" t="n">
-        <v>16350</v>
+        <v>17658</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>2546</v>
+        <v>2662</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>16705</v>
+        <v>16425</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1752</v>
+        <v>1892</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>588</v>
+        <v>601</v>
       </c>
       <c r="H28" s="14" t="n">
-        <v>759</v>
+        <v>747</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>3036</v>
+        <v>3279</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>500</v>
+        <v>556</v>
       </c>
       <c r="L28" s="14" t="n">
-        <v>665</v>
+        <v>739</v>
       </c>
     </row>
     <row r="29">
@@ -2166,37 +2166,37 @@
         </is>
       </c>
       <c r="B29" s="14" t="n">
-        <v>33569</v>
+        <v>33007</v>
       </c>
       <c r="C29" s="14" t="n">
-        <v>17211</v>
+        <v>18588</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>2680</v>
+        <v>2802</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>17584</v>
+        <v>17289</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>1844</v>
+        <v>1992</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>619</v>
+        <v>632</v>
       </c>
       <c r="H29" s="14" t="n">
-        <v>799</v>
+        <v>786</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>3196</v>
+        <v>3452</v>
       </c>
       <c r="J29" s="14" t="n">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="K29" s="14" t="n">
-        <v>527</v>
+        <v>586</v>
       </c>
       <c r="L29" s="14" t="n">
-        <v>824</v>
+        <v>916</v>
       </c>
     </row>
     <row r="30">
@@ -2206,37 +2206,37 @@
         </is>
       </c>
       <c r="B30" s="14" t="n">
-        <v>33569</v>
+        <v>33007</v>
       </c>
       <c r="C30" s="14" t="n">
-        <v>17211</v>
+        <v>18588</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>2680</v>
+        <v>2802</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>17584</v>
+        <v>17289</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>1844</v>
+        <v>1992</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>619</v>
+        <v>632</v>
       </c>
       <c r="H30" s="14" t="n">
-        <v>799</v>
+        <v>786</v>
       </c>
       <c r="I30" s="14" t="n">
-        <v>3196</v>
+        <v>3452</v>
       </c>
       <c r="J30" s="14" t="n">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>527</v>
+        <v>586</v>
       </c>
       <c r="L30" s="14" t="n">
-        <v>824</v>
+        <v>916</v>
       </c>
     </row>
     <row r="31">
@@ -2246,37 +2246,37 @@
         </is>
       </c>
       <c r="B31" s="14" t="n">
-        <v>29190</v>
+        <v>28701</v>
       </c>
       <c r="C31" s="14" t="n">
-        <v>14966</v>
+        <v>16163</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>2331</v>
+        <v>2436</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>15290</v>
+        <v>15034</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>1603</v>
+        <v>1732</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="H31" s="14" t="n">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>2779</v>
+        <v>3002</v>
       </c>
       <c r="J31" s="14" t="n">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="K31" s="14" t="n">
-        <v>458</v>
+        <v>509</v>
       </c>
       <c r="L31" s="14" t="n">
-        <v>717</v>
+        <v>796</v>
       </c>
     </row>
     <row r="32">
@@ -2286,37 +2286,37 @@
         </is>
       </c>
       <c r="B32" s="14" t="n">
-        <v>17514</v>
+        <v>17221</v>
       </c>
       <c r="C32" s="14" t="n">
-        <v>8980</v>
+        <v>9698</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>1398</v>
+        <v>1462</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>9174</v>
+        <v>9020</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>962</v>
+        <v>1039</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="H32" s="14" t="n">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="I32" s="14" t="n">
-        <v>1668</v>
+        <v>1801</v>
       </c>
       <c r="J32" s="14" t="n">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="L32" s="14" t="n">
-        <v>430</v>
+        <v>478</v>
       </c>
     </row>
     <row r="33">
@@ -2509,46 +2509,46 @@
         <v>2027</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>938235.08</v>
+        <v>958860.62</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>571098.23</v>
+        <v>571552.73</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>90435.92999999999</v>
+        <v>83383.78</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>416993.37</v>
+        <v>402686.85</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>46231.76</v>
+        <v>39944.08</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>15870.06</v>
+        <v>12715.36</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>21187.58</v>
+        <v>20169.82</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>105913.1</v>
+        <v>113761.75</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>12100.4</v>
+        <v>10973.29</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>197210.27</v>
+        <v>221984.95</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>334724.22</v>
+        <v>313966.78</v>
       </c>
       <c r="N5" s="5" t="n">
         <v>2750000</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>97.7</v>
+        <v>100.5</v>
       </c>
       <c r="P5" s="10" t="n">
-        <v>0.4717886866871852</v>
+        <v>0.4854075055668303</v>
       </c>
     </row>
     <row r="6">
@@ -2559,46 +2559,46 @@
         <v>2028</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1194671.74</v>
+        <v>1222637.81</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>793659.4300000001</v>
+        <v>795457.13</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>133220.29</v>
+        <v>123017.72</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>530965.22</v>
+        <v>513463.75</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>64248.62</v>
+        <v>55592.07</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>23378.04</v>
+        <v>18759.23</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>33713.23</v>
+        <v>32144.15</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>168526.7</v>
+        <v>181299.37</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>21343.83</v>
+        <v>19387.43</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>295854.4</v>
+        <v>333529.84</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>590418.5</v>
+        <v>554711.51</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>3850000</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>134.8</v>
+        <v>139.6</v>
       </c>
       <c r="P6" s="10" t="n">
-        <v>0.6513621143648169</v>
+        <v>0.6744062597520922</v>
       </c>
     </row>
     <row r="7">
@@ -2609,46 +2609,46 @@
         <v>2029</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1407025.38</v>
+        <v>1441217.23</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>983703.42</v>
+        <v>986718.73</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>170210.57</v>
+        <v>157293.5</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>625344.61</v>
+        <v>605259.22</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>79633.13</v>
+        <v>68958.75999999999</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>29869.24</v>
+        <v>23986.01</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>44667.47</v>
+        <v>42618.25</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>223285.06</v>
+        <v>240375.36</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>29511.1</v>
+        <v>26822.93</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>381406.42</v>
+        <v>430294.43</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>816343.58</v>
+        <v>767455.5699999999</v>
       </c>
       <c r="N7" s="15" t="n">
         <v>4791000</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>166.5</v>
+        <v>173</v>
       </c>
       <c r="P7" s="10" t="n">
-        <v>0.8044393554213264</v>
+        <v>0.8357812525389168</v>
       </c>
     </row>
     <row r="8">
@@ -2659,46 +2659,46 @@
         <v>2030</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1407025.38</v>
+        <v>1441217.23</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>983703.42</v>
+        <v>986718.73</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>170210.57</v>
+        <v>157293.5</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>625344.61</v>
+        <v>605259.22</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>79633.13</v>
+        <v>68958.75999999999</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>29869.24</v>
+        <v>23986.01</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>44667.47</v>
+        <v>42618.25</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>223285.06</v>
+        <v>240375.36</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>29511.1</v>
+        <v>26822.93</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>381406.42</v>
+        <v>430294.43</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>816343.58</v>
+        <v>767455.5699999999</v>
       </c>
       <c r="N8" s="15" t="n">
         <v>4791000</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>166.5</v>
+        <v>173</v>
       </c>
       <c r="P8" s="10" t="n">
-        <v>0.8044393554213264</v>
+        <v>0.8357812525389168</v>
       </c>
     </row>
     <row r="9">
@@ -2709,46 +2709,46 @@
         <v>2031</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1407025.38</v>
+        <v>1441217.23</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>983703.42</v>
+        <v>986718.73</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>170210.57</v>
+        <v>157293.5</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>625344.61</v>
+        <v>605259.22</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>79633.13</v>
+        <v>68958.75999999999</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>29869.24</v>
+        <v>23986.01</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>44667.47</v>
+        <v>42618.25</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>223285.06</v>
+        <v>240375.36</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>29511.1</v>
+        <v>26822.93</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>381406.42</v>
+        <v>430294.43</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>816343.58</v>
+        <v>767455.5699999999</v>
       </c>
       <c r="N9" s="15" t="n">
         <v>4791000</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>166.5</v>
+        <v>173</v>
       </c>
       <c r="P9" s="10" t="n">
-        <v>0.8044393554213264</v>
+        <v>0.8357812525389168</v>
       </c>
     </row>
     <row r="10">
@@ -2759,46 +2759,46 @@
         <v>2032</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1407025.38</v>
+        <v>1441217.23</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>983703.42</v>
+        <v>986718.73</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>170210.57</v>
+        <v>157293.5</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>625344.61</v>
+        <v>605259.22</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>79633.13</v>
+        <v>68958.75999999999</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>29869.24</v>
+        <v>23986.01</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>44667.47</v>
+        <v>42618.25</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>223285.06</v>
+        <v>240375.36</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>29511.1</v>
+        <v>26822.93</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>381406.42</v>
+        <v>430294.43</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>816343.58</v>
+        <v>767455.5699999999</v>
       </c>
       <c r="N10" s="15" t="n">
         <v>4791000</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>166.5</v>
+        <v>173</v>
       </c>
       <c r="P10" s="10" t="n">
-        <v>0.8044393554213264</v>
+        <v>0.8357812525389168</v>
       </c>
     </row>
     <row r="11">
@@ -2809,46 +2809,46 @@
         <v>2033</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1407025.38</v>
+        <v>1441217.23</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>983703.42</v>
+        <v>986718.73</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>170210.57</v>
+        <v>157293.5</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>625344.61</v>
+        <v>605259.22</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>79633.13</v>
+        <v>68958.75999999999</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>29869.24</v>
+        <v>23986.01</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>44667.47</v>
+        <v>42618.25</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>223285.06</v>
+        <v>240375.36</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>29511.1</v>
+        <v>26822.93</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>381406.42</v>
+        <v>430294.43</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>816343.58</v>
+        <v>767455.5699999999</v>
       </c>
       <c r="N11" s="15" t="n">
         <v>4791000</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>166.5</v>
+        <v>173</v>
       </c>
       <c r="P11" s="10" t="n">
-        <v>0.8044393554213264</v>
+        <v>0.8357812525389168</v>
       </c>
     </row>
     <row r="12">
@@ -2859,46 +2859,46 @@
         <v>2034</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>1407025.38</v>
+        <v>1441217.23</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>983703.42</v>
+        <v>986718.73</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>170210.57</v>
+        <v>157293.5</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>625344.61</v>
+        <v>605259.22</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>79633.13</v>
+        <v>68958.75999999999</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>29869.24</v>
+        <v>23986.01</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>44667.47</v>
+        <v>42618.25</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>223285.06</v>
+        <v>240375.36</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>29511.1</v>
+        <v>26822.93</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>381406.42</v>
+        <v>430294.43</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>816343.58</v>
+        <v>767455.5699999999</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>4791000</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>166.5</v>
+        <v>173</v>
       </c>
       <c r="P12" s="10" t="n">
-        <v>0.8044393554213264</v>
+        <v>0.8357812525389168</v>
       </c>
     </row>
     <row r="13">
@@ -2909,46 +2909,46 @@
         <v>2035</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1407025.38</v>
+        <v>1441217.23</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>983703.42</v>
+        <v>986718.73</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>170210.57</v>
+        <v>157293.5</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>625344.61</v>
+        <v>605259.22</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>79633.13</v>
+        <v>68958.75999999999</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>29869.24</v>
+        <v>23986.01</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>44667.47</v>
+        <v>42618.25</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>223285.06</v>
+        <v>240375.36</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>29511.1</v>
+        <v>26822.93</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>381406.42</v>
+        <v>430294.43</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>816343.58</v>
+        <v>767455.5699999999</v>
       </c>
       <c r="N13" s="15" t="n">
         <v>4791000</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>166.5</v>
+        <v>173</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>0.8044393554213264</v>
+        <v>0.8357812525389168</v>
       </c>
     </row>
     <row r="14">
@@ -2959,46 +2959,46 @@
         <v>2036</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>1407025.38</v>
+        <v>1441217.23</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>983703.42</v>
+        <v>986718.73</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>170210.57</v>
+        <v>157293.5</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>625344.61</v>
+        <v>605259.22</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>79633.13</v>
+        <v>68958.75999999999</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>29869.24</v>
+        <v>23986.01</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>44667.47</v>
+        <v>42618.25</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>223285.06</v>
+        <v>240375.36</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>29511.1</v>
+        <v>26822.93</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>381406.42</v>
+        <v>430294.43</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>816343.58</v>
+        <v>767455.5699999999</v>
       </c>
       <c r="N14" s="15" t="n">
         <v>4791000</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>166.5</v>
+        <v>173</v>
       </c>
       <c r="P14" s="10" t="n">
-        <v>0.8044393554213264</v>
+        <v>0.8357812525389168</v>
       </c>
     </row>
     <row r="15">
@@ -3009,46 +3009,46 @@
         <v>2037</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1407025.38</v>
+        <v>1441217.23</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>983703.42</v>
+        <v>986718.73</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>170210.57</v>
+        <v>157293.5</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>625344.61</v>
+        <v>605259.22</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>79633.13</v>
+        <v>68958.75999999999</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>29869.24</v>
+        <v>23986.01</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>44667.47</v>
+        <v>42618.25</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>223285.06</v>
+        <v>240375.36</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>29511.1</v>
+        <v>26822.93</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>381406.42</v>
+        <v>430294.43</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>816343.58</v>
+        <v>767455.5699999999</v>
       </c>
       <c r="N15" s="15" t="n">
         <v>4791000</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>166.5</v>
+        <v>173</v>
       </c>
       <c r="P15" s="10" t="n">
-        <v>0.8044393554213264</v>
+        <v>0.8357812525389168</v>
       </c>
     </row>
     <row r="16">
@@ -3059,46 +3059,46 @@
         <v>2038</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>1407025.38</v>
+        <v>1441217.23</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>983703.42</v>
+        <v>986718.73</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>170210.57</v>
+        <v>157293.5</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>625344.61</v>
+        <v>605259.22</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>79633.13</v>
+        <v>68958.75999999999</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>29869.24</v>
+        <v>23986.01</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>44667.47</v>
+        <v>42618.25</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>223285.06</v>
+        <v>240375.36</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>29511.1</v>
+        <v>26822.93</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>381406.42</v>
+        <v>430294.43</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>816343.58</v>
+        <v>767455.5699999999</v>
       </c>
       <c r="N16" s="15" t="n">
         <v>4791000</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>166.5</v>
+        <v>173</v>
       </c>
       <c r="P16" s="10" t="n">
-        <v>0.8044393554213264</v>
+        <v>0.8357812525389168</v>
       </c>
     </row>
     <row r="17">
@@ -3110,57 +3110,57 @@
       <c r="B17" s="13" t="n"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>34.1% / 31.0% / 29.4%</t>
+          <t>34.9% / 31.8% / 30.1%</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>20.8% / 20.6% / 20.5%</t>
+          <t>20.8% / 20.7% / 20.6%</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>3.3% / 3.5% / 3.6%</t>
+          <t>3.0% / 3.2% / 3.3%</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>15.2% / 13.8% / 13.1%</t>
+          <t>14.6% / 13.3% / 12.6%</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>1.7% / 1.7% / 1.7%</t>
+          <t>1.5% / 1.4% / 1.4%</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>0.6% / 0.6% / 0.6%</t>
+          <t>0.5% / 0.5% / 0.5%</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>0.8% / 0.9% / 0.9%</t>
+          <t>0.7% / 0.8% / 0.9%</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>3.9% / 4.4% / 4.7%</t>
+          <t>4.1% / 4.7% / 5.0%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>0.4% / 0.6% / 0.6%</t>
+          <t>0.4% / 0.5% / 0.6%</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>7.2% / 7.7% / 8.0%</t>
+          <t>8.1% / 8.7% / 9.0%</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
-          <t>12.2% / 15.3% / 17.0%</t>
+          <t>11.4% / 14.4% / 16.0%</t>
         </is>
       </c>
     </row>
@@ -3843,12 +3843,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>97.7 de 207</t>
+          <t>100.5 de 207</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>✓ 47% da capacidade efetiva</t>
+          <t>✓ 49% da capacidade efetiva</t>
         </is>
       </c>
     </row>
@@ -3860,12 +3860,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>134.8 de 207</t>
+          <t>139.6 de 207</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>✓ 65%</t>
+          <t>✓ 67%</t>
         </is>
       </c>
     </row>
@@ -3877,12 +3877,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>166.5 de 207</t>
+          <t>173.0 de 207</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>✓ 80% (§3.7)</t>
+          <t>✓ 84% (§3.7)</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>76.0% da capacidade mensal</t>
+          <t>78.8% da capacidade mensal</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>R$ 496.308</t>
+          <t>R$ 477.697</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">

--- a/estudo-mercado-gtk/dossie-bnb/previsao-faturamento.xlsx
+++ b/estudo-mercado-gtk/dossie-bnb/previsao-faturamento.xlsx
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>31452.59</v>
+        <v>31423.67</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>53469.4</v>
+        <v>53420.25</v>
       </c>
       <c r="D11" s="6" t="inlineStr"/>
     </row>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>105506.7</v>
+        <v>105263.22</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>153037.92</v>
+        <v>155958.4</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>208605.48</v>
+        <v>213699.38</v>
       </c>
       <c r="D14" s="6" t="inlineStr"/>
     </row>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>267968.87</v>
+        <v>269493.96</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>305003.32</v>
+        <v>306313.94</v>
       </c>
       <c r="D16" s="6" t="inlineStr"/>
     </row>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>348640.78</v>
+        <v>347928.49</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>376349.28</v>
+        <v>373454.74</v>
       </c>
       <c r="D18" s="6" t="inlineStr"/>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>376349.28</v>
+        <v>373454.74</v>
       </c>
       <c r="D19" s="6" t="inlineStr"/>
     </row>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>327260.24</v>
+        <v>324743.25</v>
       </c>
       <c r="D20" s="6" t="inlineStr"/>
     </row>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>196356.15</v>
+        <v>194845.95</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>22150.27</v>
+        <v>23076.94</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>0</v>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>9302.309999999999</v>
+        <v>8346.73</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -1092,16 +1092,16 @@
         <v>0</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>31452.59</v>
+        <v>31423.67</v>
       </c>
       <c r="N5" s="9" t="n">
         <v>1.2</v>
       </c>
       <c r="O5" s="10" t="n">
-        <v>0.06584215689850713</v>
+        <v>0.06595027677078899</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>31452.59</v>
+        <v>31423.67</v>
       </c>
     </row>
     <row r="6">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>37655.46</v>
+        <v>39230.8</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>0</v>
@@ -1120,7 +1120,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>15813.93</v>
+        <v>14189.44</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -1144,16 +1144,16 @@
         <v>0</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>53469.4</v>
+        <v>53420.25</v>
       </c>
       <c r="N6" s="9" t="n">
         <v>2.1</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>0.1119316667274621</v>
+        <v>0.1121154705103413</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>84921.98</v>
+        <v>84843.92</v>
       </c>
     </row>
     <row r="7">
@@ -1163,19 +1163,19 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>59067.39</v>
+        <v>61538.51</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>20220.03</v>
+        <v>20064.51</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>24806.17</v>
+        <v>22257.95</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1413.12</v>
+        <v>1402.25</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0</v>
@@ -1196,16 +1196,16 @@
         <v>0</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>105506.7</v>
+        <v>105263.22</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O7" s="10" t="n">
-        <v>0.2208654326700041</v>
+        <v>0.220920656868999</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>190428.68</v>
+        <v>190107.14</v>
       </c>
     </row>
     <row r="8">
@@ -1215,22 +1215,22 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>72357.55</v>
+        <v>75384.67999999999</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>34677.34</v>
+        <v>34410.64</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>3948.53</v>
+        <v>3838.23</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>30387.56</v>
+        <v>27265.99</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>2423.49</v>
+        <v>2404.85</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>602.12</v>
+        <v>546.39</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0</v>
@@ -1242,22 +1242,22 @@
         <v>0</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>8641.32</v>
+        <v>12107.61</v>
       </c>
       <c r="L8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>153037.92</v>
+        <v>155958.4</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O8" s="10" t="n">
-        <v>0.3203662436043561</v>
+        <v>0.327316893591964</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>343466.6</v>
+        <v>346065.54</v>
       </c>
     </row>
     <row r="9">
@@ -1267,49 +1267,49 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>86632.17</v>
+        <v>90256.49000000001</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>50415.26</v>
+        <v>50027.52</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>6618.48</v>
+        <v>6433.61</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>36382.38</v>
+        <v>32644.99</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>3523.37</v>
+        <v>3496.27</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1009.27</v>
+        <v>915.86</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>1280.9</v>
+        <v>1011.4</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>7224.53</v>
+        <v>7168.97</v>
       </c>
       <c r="J9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>15519.11</v>
+        <v>21744.28</v>
       </c>
       <c r="L9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>208605.48</v>
+        <v>213699.38</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="O9" s="10" t="n">
-        <v>0.4366901667944827</v>
+        <v>0.4485004963192685</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>552072.08</v>
+        <v>559764.92</v>
       </c>
     </row>
     <row r="10">
@@ -1319,49 +1319,49 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>92046.67999999999</v>
+        <v>95897.52</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>63019.08</v>
+        <v>62534.39</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>8539.030000000001</v>
+        <v>8300.5</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>38656.28</v>
+        <v>34685.31</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>4404.21</v>
+        <v>4370.34</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1302.13</v>
+        <v>1181.62</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>1905.34</v>
+        <v>1504.46</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>10746.49</v>
+        <v>10663.84</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>856.55</v>
+        <v>849.97</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>21985.4</v>
+        <v>30804.4</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>24507.67</v>
+        <v>18701.62</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>267968.87</v>
+        <v>269493.96</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="O10" s="10" t="n">
-        <v>0.5609601950759683</v>
+        <v>0.5655990826458925</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>820040.95</v>
+        <v>829258.88</v>
       </c>
     </row>
     <row r="11">
@@ -1371,49 +1371,49 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>97461.19</v>
+        <v>101538.55</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>66726.09</v>
+        <v>66212.89</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>10636.85</v>
+        <v>10339.73</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>40930.18</v>
+        <v>36725.62</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>4663.28</v>
+        <v>4627.42</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1622.04</v>
+        <v>1471.91</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>2449.72</v>
+        <v>1934.3</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>13816.92</v>
+        <v>13710.65</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>1269.72</v>
+        <v>1259.95</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>29098.33</v>
+        <v>40770.53</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>36329.01</v>
+        <v>27722.4</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>305003.32</v>
+        <v>306313.94</v>
       </c>
       <c r="N11" s="9" t="n">
         <v>11.1</v>
       </c>
       <c r="O11" s="10" t="n">
-        <v>0.6384873040118203</v>
+        <v>0.6428748351205847</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>1125044.27</v>
+        <v>1135572.82</v>
       </c>
     </row>
     <row r="12">
@@ -1423,49 +1423,49 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>107551.87</v>
+        <v>112051.38</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>73634.59</v>
+        <v>73068.25999999999</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>11738.14</v>
+        <v>11410.25</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>45167.9</v>
+        <v>40528.02</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>5146.1</v>
+        <v>5106.52</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1789.97</v>
+        <v>1624.3</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>3180.42</v>
+        <v>2511.26</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>17938.18</v>
+        <v>17800.22</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>1701.43</v>
+        <v>1688.34</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>32111.03</v>
+        <v>44991.72</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>48681.14</v>
+        <v>37148.21</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>348640.78</v>
+        <v>347928.49</v>
       </c>
       <c r="N12" s="9" t="n">
         <v>12.6</v>
       </c>
       <c r="O12" s="10" t="n">
-        <v>0.7298370066666164</v>
+        <v>0.730213170544197</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>1473685.05</v>
+        <v>1483501.31</v>
       </c>
     </row>
     <row r="13">
@@ -1475,49 +1475,49 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>113212.5</v>
+        <v>117948.82</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>77510.10000000001</v>
+        <v>76913.96000000001</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>12355.94</v>
+        <v>12010.79</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>47545.16</v>
+        <v>42661.07</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>5416.94</v>
+        <v>5375.28</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1884.18</v>
+        <v>1709.79</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>3347.81</v>
+        <v>2643.44</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>18882.3</v>
+        <v>18737.07</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>2107.03</v>
+        <v>2090.83</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>33801.08</v>
+        <v>47359.71</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>60286.24</v>
+        <v>46003.98</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>376349.28</v>
+        <v>373454.74</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>0.7878413867196007</v>
+        <v>0.7837862517731843</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>1850034.33</v>
+        <v>1856956.05</v>
       </c>
     </row>
     <row r="14">
@@ -1527,49 +1527,49 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>113212.5</v>
+        <v>117948.82</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>77510.10000000001</v>
+        <v>76913.96000000001</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>12355.94</v>
+        <v>12010.79</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>47545.16</v>
+        <v>42661.07</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>5416.94</v>
+        <v>5375.28</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1884.18</v>
+        <v>1709.79</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>3347.81</v>
+        <v>2643.44</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>18882.3</v>
+        <v>18737.07</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>2107.03</v>
+        <v>2090.83</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>33801.08</v>
+        <v>47359.71</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>60286.24</v>
+        <v>46003.98</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>376349.28</v>
+        <v>373454.74</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="O14" s="10" t="n">
-        <v>0.7878413867196007</v>
+        <v>0.7837862517731843</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>2226383.61</v>
+        <v>2230410.79</v>
       </c>
     </row>
     <row r="15">
@@ -1579,49 +1579,49 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>98445.64999999999</v>
+        <v>102564.19</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>67400.09</v>
+        <v>66881.71000000001</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>10744.29</v>
+        <v>10444.17</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>41343.62</v>
+        <v>37096.58</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>4710.39</v>
+        <v>4674.16</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1638.42</v>
+        <v>1486.78</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>2911.14</v>
+        <v>2298.64</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>16419.39</v>
+        <v>16293.11</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>1832.2</v>
+        <v>1818.11</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>29392.25</v>
+        <v>41182.35</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>52422.81</v>
+        <v>40003.46</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>327260.24</v>
+        <v>324743.25</v>
       </c>
       <c r="N15" s="9" t="n">
         <v>11.8</v>
       </c>
       <c r="O15" s="10" t="n">
-        <v>0.6850794667126963</v>
+        <v>0.6815532624114647</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>2553643.85</v>
+        <v>2555154.05</v>
       </c>
     </row>
     <row r="16">
@@ -1631,46 +1631,46 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>59067.39</v>
+        <v>61538.51</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>40440.05</v>
+        <v>40129.02</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>6446.58</v>
+        <v>6266.5</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>24806.17</v>
+        <v>22257.95</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>2826.23</v>
+        <v>2804.49</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>983.05</v>
+        <v>892.0700000000001</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>1746.68</v>
+        <v>1379.18</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>9851.629999999999</v>
+        <v>9775.860000000001</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>1099.32</v>
+        <v>1090.87</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>17635.35</v>
+        <v>24709.41</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>31453.69</v>
+        <v>24002.08</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>196356.15</v>
+        <v>194845.95</v>
       </c>
       <c r="N16" s="9" t="n">
         <v>7.1</v>
       </c>
       <c r="O16" s="10" t="n">
-        <v>0.4110476800276178</v>
+        <v>0.4089319574468789</v>
       </c>
       <c r="P16" s="5" t="n">
         <v>2750000</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="B21" s="14" t="n">
-        <v>6458</v>
+        <v>6728</v>
       </c>
       <c r="C21" s="14" t="n">
         <v>0</v>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>3383</v>
+        <v>3035</v>
       </c>
       <c r="F21" s="14" t="n">
         <v>0</v>
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="B22" s="14" t="n">
-        <v>10978</v>
+        <v>11438</v>
       </c>
       <c r="C22" s="14" t="n">
         <v>0</v>
@@ -1895,7 +1895,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>5751</v>
+        <v>5160</v>
       </c>
       <c r="F22" s="14" t="n">
         <v>0</v>
@@ -1926,19 +1926,19 @@
         </is>
       </c>
       <c r="B23" s="14" t="n">
-        <v>17221</v>
+        <v>17941</v>
       </c>
       <c r="C23" s="14" t="n">
-        <v>4849</v>
+        <v>4812</v>
       </c>
       <c r="D23" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>9020</v>
+        <v>8094</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>0</v>
@@ -1966,22 +1966,22 @@
         </is>
       </c>
       <c r="B24" s="14" t="n">
-        <v>21095</v>
+        <v>21978</v>
       </c>
       <c r="C24" s="14" t="n">
-        <v>8316</v>
+        <v>8252</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>895</v>
+        <v>870</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>11050</v>
+        <v>9915</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>891</v>
+        <v>884</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="H24" s="14" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="L24" s="14" t="n">
         <v>0</v>
@@ -2006,34 +2006,34 @@
         </is>
       </c>
       <c r="B25" s="14" t="n">
-        <v>25257</v>
+        <v>26314</v>
       </c>
       <c r="C25" s="14" t="n">
-        <v>12090</v>
+        <v>11997</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>1501</v>
+        <v>1459</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>13230</v>
+        <v>11871</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>1295</v>
+        <v>1285</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>339</v>
+        <v>307</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>301</v>
+        <v>237</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>1321</v>
+        <v>1311</v>
       </c>
       <c r="J25" s="14" t="n">
         <v>0</v>
       </c>
       <c r="K25" s="14" t="n">
-        <v>269</v>
+        <v>377</v>
       </c>
       <c r="L25" s="14" t="n">
         <v>0</v>
@@ -2046,37 +2046,37 @@
         </is>
       </c>
       <c r="B26" s="14" t="n">
-        <v>26836</v>
+        <v>27958</v>
       </c>
       <c r="C26" s="14" t="n">
-        <v>15112</v>
+        <v>14996</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>1936</v>
+        <v>1882</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>14057</v>
+        <v>12613</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>1619</v>
+        <v>1607</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>437</v>
+        <v>397</v>
       </c>
       <c r="H26" s="14" t="n">
-        <v>447</v>
+        <v>353</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>1965</v>
+        <v>1950</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>381</v>
+        <v>534</v>
       </c>
       <c r="L26" s="14" t="n">
-        <v>372</v>
+        <v>284</v>
       </c>
     </row>
     <row r="27">
@@ -2086,37 +2086,37 @@
         </is>
       </c>
       <c r="B27" s="14" t="n">
-        <v>28414</v>
+        <v>29603</v>
       </c>
       <c r="C27" s="14" t="n">
-        <v>16001</v>
+        <v>15878</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>2412</v>
+        <v>2345</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>14884</v>
+        <v>13355</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>1714</v>
+        <v>1701</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>544</v>
+        <v>494</v>
       </c>
       <c r="H27" s="14" t="n">
-        <v>575</v>
+        <v>454</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>2526</v>
+        <v>2507</v>
       </c>
       <c r="J27" s="14" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="K27" s="14" t="n">
-        <v>504</v>
+        <v>706</v>
       </c>
       <c r="L27" s="14" t="n">
-        <v>552</v>
+        <v>421</v>
       </c>
     </row>
     <row r="28">
@@ -2126,37 +2126,37 @@
         </is>
       </c>
       <c r="B28" s="14" t="n">
-        <v>31356</v>
+        <v>32668</v>
       </c>
       <c r="C28" s="14" t="n">
-        <v>17658</v>
+        <v>17522</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>2662</v>
+        <v>2587</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>16425</v>
+        <v>14737</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1892</v>
+        <v>1877</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>601</v>
+        <v>545</v>
       </c>
       <c r="H28" s="14" t="n">
-        <v>747</v>
+        <v>589</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>3279</v>
+        <v>3254</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>556</v>
+        <v>779</v>
       </c>
       <c r="L28" s="14" t="n">
-        <v>739</v>
+        <v>564</v>
       </c>
     </row>
     <row r="29">
@@ -2166,37 +2166,37 @@
         </is>
       </c>
       <c r="B29" s="14" t="n">
-        <v>33007</v>
+        <v>34387</v>
       </c>
       <c r="C29" s="14" t="n">
-        <v>18588</v>
+        <v>18445</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>2802</v>
+        <v>2724</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>17289</v>
+        <v>15513</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>1992</v>
+        <v>1976</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>632</v>
+        <v>574</v>
       </c>
       <c r="H29" s="14" t="n">
-        <v>786</v>
+        <v>621</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>3452</v>
+        <v>3425</v>
       </c>
       <c r="J29" s="14" t="n">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="K29" s="14" t="n">
-        <v>586</v>
+        <v>820</v>
       </c>
       <c r="L29" s="14" t="n">
-        <v>916</v>
+        <v>699</v>
       </c>
     </row>
     <row r="30">
@@ -2206,37 +2206,37 @@
         </is>
       </c>
       <c r="B30" s="14" t="n">
-        <v>33007</v>
+        <v>34387</v>
       </c>
       <c r="C30" s="14" t="n">
-        <v>18588</v>
+        <v>18445</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>2802</v>
+        <v>2724</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>17289</v>
+        <v>15513</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>1992</v>
+        <v>1976</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>632</v>
+        <v>574</v>
       </c>
       <c r="H30" s="14" t="n">
-        <v>786</v>
+        <v>621</v>
       </c>
       <c r="I30" s="14" t="n">
-        <v>3452</v>
+        <v>3425</v>
       </c>
       <c r="J30" s="14" t="n">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>586</v>
+        <v>820</v>
       </c>
       <c r="L30" s="14" t="n">
-        <v>916</v>
+        <v>699</v>
       </c>
     </row>
     <row r="31">
@@ -2246,37 +2246,37 @@
         </is>
       </c>
       <c r="B31" s="14" t="n">
-        <v>28701</v>
+        <v>29902</v>
       </c>
       <c r="C31" s="14" t="n">
-        <v>16163</v>
+        <v>16039</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>2436</v>
+        <v>2368</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>15034</v>
+        <v>13490</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>1732</v>
+        <v>1718</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>550</v>
+        <v>499</v>
       </c>
       <c r="H31" s="14" t="n">
-        <v>683</v>
+        <v>540</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>3002</v>
+        <v>2979</v>
       </c>
       <c r="J31" s="14" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="K31" s="14" t="n">
-        <v>509</v>
+        <v>713</v>
       </c>
       <c r="L31" s="14" t="n">
-        <v>796</v>
+        <v>608</v>
       </c>
     </row>
     <row r="32">
@@ -2286,37 +2286,37 @@
         </is>
       </c>
       <c r="B32" s="14" t="n">
-        <v>17221</v>
+        <v>17941</v>
       </c>
       <c r="C32" s="14" t="n">
-        <v>9698</v>
+        <v>9623</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>1462</v>
+        <v>1421</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>9020</v>
+        <v>8094</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>1039</v>
+        <v>1031</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>330</v>
+        <v>299</v>
       </c>
       <c r="H32" s="14" t="n">
-        <v>410</v>
+        <v>324</v>
       </c>
       <c r="I32" s="14" t="n">
-        <v>1801</v>
+        <v>1787</v>
       </c>
       <c r="J32" s="14" t="n">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>305</v>
+        <v>428</v>
       </c>
       <c r="L32" s="14" t="n">
-        <v>478</v>
+        <v>365</v>
       </c>
     </row>
     <row r="33">
@@ -2509,46 +2509,46 @@
         <v>2027</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>958860.62</v>
+        <v>998975.1899999999</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>571552.73</v>
+        <v>567156.86</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>83383.78</v>
+        <v>81054.58</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>402686.85</v>
+        <v>361320.74</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>39944.08</v>
+        <v>39636.86</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>12715.36</v>
+        <v>11538.51</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>20169.82</v>
+        <v>15926.12</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>113761.75</v>
+        <v>112886.8</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>10973.29</v>
+        <v>10888.89</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>221984.95</v>
+        <v>311029.73</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>313966.78</v>
+        <v>239585.72</v>
       </c>
       <c r="N5" s="5" t="n">
         <v>2750000</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>100.5</v>
+        <v>100.7</v>
       </c>
       <c r="P5" s="10" t="n">
-        <v>0.4854075055668303</v>
+        <v>0.4865031957506592</v>
       </c>
     </row>
     <row r="6">
@@ -2559,46 +2559,46 @@
         <v>2028</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1222637.81</v>
+        <v>1279866.47</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>795457.13</v>
+        <v>793303.15</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>123017.72</v>
+        <v>120200.43</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>513463.75</v>
+        <v>462916.7</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>55592.07</v>
+        <v>55441.54</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>18759.23</v>
+        <v>17111.11</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>32144.15</v>
+        <v>25517.32</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>181299.37</v>
+        <v>180870.64</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>19387.43</v>
+        <v>19346.07</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>333529.84</v>
+        <v>469759.41</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>554711.51</v>
+        <v>425667.16</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>3850000</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>139.6</v>
+        <v>139.9</v>
       </c>
       <c r="P6" s="10" t="n">
-        <v>0.6744062597520922</v>
+        <v>0.6760623351892264</v>
       </c>
     </row>
     <row r="7">
@@ -2609,25 +2609,25 @@
         <v>2029</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1441217.23</v>
+        <v>1513149.29</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>986718.73</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>157293.5</v>
+        <v>154084.85</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>605259.22</v>
+        <v>547293.09</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>68958.75999999999</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>23986.01</v>
+        <v>21934.72</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>42618.25</v>
+        <v>33912.27</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>240375.36</v>
@@ -2636,19 +2636,19 @@
         <v>26822.93</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>430294.43</v>
+        <v>607571.24</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>767455.5699999999</v>
+        <v>590178.76</v>
       </c>
       <c r="N7" s="15" t="n">
         <v>4791000</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>173</v>
+        <v>173.5</v>
       </c>
       <c r="P7" s="10" t="n">
-        <v>0.8357812525389168</v>
+        <v>0.8379239203114061</v>
       </c>
     </row>
     <row r="8">
@@ -2659,25 +2659,25 @@
         <v>2030</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1441217.23</v>
+        <v>1513149.29</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>986718.73</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>157293.5</v>
+        <v>154084.85</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>605259.22</v>
+        <v>547293.09</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>68958.75999999999</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>23986.01</v>
+        <v>21934.72</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>42618.25</v>
+        <v>33912.27</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>240375.36</v>
@@ -2686,19 +2686,19 @@
         <v>26822.93</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>430294.43</v>
+        <v>607571.24</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>767455.5699999999</v>
+        <v>590178.76</v>
       </c>
       <c r="N8" s="15" t="n">
         <v>4791000</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>173</v>
+        <v>173.5</v>
       </c>
       <c r="P8" s="10" t="n">
-        <v>0.8357812525389168</v>
+        <v>0.8379239203114061</v>
       </c>
     </row>
     <row r="9">
@@ -2709,25 +2709,25 @@
         <v>2031</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1441217.23</v>
+        <v>1513149.29</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>986718.73</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>157293.5</v>
+        <v>154084.85</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>605259.22</v>
+        <v>547293.09</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>68958.75999999999</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>23986.01</v>
+        <v>21934.72</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>42618.25</v>
+        <v>33912.27</v>
       </c>
       <c r="J9" s="5" t="n">
         <v>240375.36</v>
@@ -2736,19 +2736,19 @@
         <v>26822.93</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>430294.43</v>
+        <v>607571.24</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>767455.5699999999</v>
+        <v>590178.76</v>
       </c>
       <c r="N9" s="15" t="n">
         <v>4791000</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>173</v>
+        <v>173.5</v>
       </c>
       <c r="P9" s="10" t="n">
-        <v>0.8357812525389168</v>
+        <v>0.8379239203114061</v>
       </c>
     </row>
     <row r="10">
@@ -2759,25 +2759,25 @@
         <v>2032</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1441217.23</v>
+        <v>1513149.29</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>986718.73</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>157293.5</v>
+        <v>154084.85</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>605259.22</v>
+        <v>547293.09</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>68958.75999999999</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>23986.01</v>
+        <v>21934.72</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>42618.25</v>
+        <v>33912.27</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>240375.36</v>
@@ -2786,19 +2786,19 @@
         <v>26822.93</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>430294.43</v>
+        <v>607571.24</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>767455.5699999999</v>
+        <v>590178.76</v>
       </c>
       <c r="N10" s="15" t="n">
         <v>4791000</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>173</v>
+        <v>173.5</v>
       </c>
       <c r="P10" s="10" t="n">
-        <v>0.8357812525389168</v>
+        <v>0.8379239203114061</v>
       </c>
     </row>
     <row r="11">
@@ -2809,25 +2809,25 @@
         <v>2033</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1441217.23</v>
+        <v>1513149.29</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>986718.73</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>157293.5</v>
+        <v>154084.85</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>605259.22</v>
+        <v>547293.09</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>68958.75999999999</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>23986.01</v>
+        <v>21934.72</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>42618.25</v>
+        <v>33912.27</v>
       </c>
       <c r="J11" s="5" t="n">
         <v>240375.36</v>
@@ -2836,19 +2836,19 @@
         <v>26822.93</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>430294.43</v>
+        <v>607571.24</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>767455.5699999999</v>
+        <v>590178.76</v>
       </c>
       <c r="N11" s="15" t="n">
         <v>4791000</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>173</v>
+        <v>173.5</v>
       </c>
       <c r="P11" s="10" t="n">
-        <v>0.8357812525389168</v>
+        <v>0.8379239203114061</v>
       </c>
     </row>
     <row r="12">
@@ -2859,25 +2859,25 @@
         <v>2034</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>1441217.23</v>
+        <v>1513149.29</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>986718.73</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>157293.5</v>
+        <v>154084.85</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>605259.22</v>
+        <v>547293.09</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>68958.75999999999</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>23986.01</v>
+        <v>21934.72</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>42618.25</v>
+        <v>33912.27</v>
       </c>
       <c r="J12" s="5" t="n">
         <v>240375.36</v>
@@ -2886,19 +2886,19 @@
         <v>26822.93</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>430294.43</v>
+        <v>607571.24</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>767455.5699999999</v>
+        <v>590178.76</v>
       </c>
       <c r="N12" s="15" t="n">
         <v>4791000</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>173</v>
+        <v>173.5</v>
       </c>
       <c r="P12" s="10" t="n">
-        <v>0.8357812525389168</v>
+        <v>0.8379239203114061</v>
       </c>
     </row>
     <row r="13">
@@ -2909,25 +2909,25 @@
         <v>2035</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1441217.23</v>
+        <v>1513149.29</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>986718.73</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>157293.5</v>
+        <v>154084.85</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>605259.22</v>
+        <v>547293.09</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>68958.75999999999</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>23986.01</v>
+        <v>21934.72</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>42618.25</v>
+        <v>33912.27</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>240375.36</v>
@@ -2936,19 +2936,19 @@
         <v>26822.93</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>430294.43</v>
+        <v>607571.24</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>767455.5699999999</v>
+        <v>590178.76</v>
       </c>
       <c r="N13" s="15" t="n">
         <v>4791000</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>173</v>
+        <v>173.5</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>0.8357812525389168</v>
+        <v>0.8379239203114061</v>
       </c>
     </row>
     <row r="14">
@@ -2959,25 +2959,25 @@
         <v>2036</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>1441217.23</v>
+        <v>1513149.29</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>986718.73</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>157293.5</v>
+        <v>154084.85</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>605259.22</v>
+        <v>547293.09</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>68958.75999999999</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>23986.01</v>
+        <v>21934.72</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>42618.25</v>
+        <v>33912.27</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>240375.36</v>
@@ -2986,19 +2986,19 @@
         <v>26822.93</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>430294.43</v>
+        <v>607571.24</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>767455.5699999999</v>
+        <v>590178.76</v>
       </c>
       <c r="N14" s="15" t="n">
         <v>4791000</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>173</v>
+        <v>173.5</v>
       </c>
       <c r="P14" s="10" t="n">
-        <v>0.8357812525389168</v>
+        <v>0.8379239203114061</v>
       </c>
     </row>
     <row r="15">
@@ -3009,25 +3009,25 @@
         <v>2037</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1441217.23</v>
+        <v>1513149.29</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>986718.73</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>157293.5</v>
+        <v>154084.85</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>605259.22</v>
+        <v>547293.09</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>68958.75999999999</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>23986.01</v>
+        <v>21934.72</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>42618.25</v>
+        <v>33912.27</v>
       </c>
       <c r="J15" s="5" t="n">
         <v>240375.36</v>
@@ -3036,19 +3036,19 @@
         <v>26822.93</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>430294.43</v>
+        <v>607571.24</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>767455.5699999999</v>
+        <v>590178.76</v>
       </c>
       <c r="N15" s="15" t="n">
         <v>4791000</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>173</v>
+        <v>173.5</v>
       </c>
       <c r="P15" s="10" t="n">
-        <v>0.8357812525389168</v>
+        <v>0.8379239203114061</v>
       </c>
     </row>
     <row r="16">
@@ -3059,25 +3059,25 @@
         <v>2038</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>1441217.23</v>
+        <v>1513149.29</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>986718.73</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>157293.5</v>
+        <v>154084.85</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>605259.22</v>
+        <v>547293.09</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>68958.75999999999</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>23986.01</v>
+        <v>21934.72</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>42618.25</v>
+        <v>33912.27</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>240375.36</v>
@@ -3086,19 +3086,19 @@
         <v>26822.93</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>430294.43</v>
+        <v>607571.24</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>767455.5699999999</v>
+        <v>590178.76</v>
       </c>
       <c r="N16" s="15" t="n">
         <v>4791000</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>173</v>
+        <v>173.5</v>
       </c>
       <c r="P16" s="10" t="n">
-        <v>0.8357812525389168</v>
+        <v>0.8379239203114061</v>
       </c>
     </row>
     <row r="17">
@@ -3110,37 +3110,37 @@
       <c r="B17" s="13" t="n"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>34.9% / 31.8% / 30.1%</t>
+          <t>36.3% / 33.2% / 31.6%</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>20.8% / 20.7% / 20.6%</t>
+          <t>20.6% / 20.6% / 20.6%</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>3.0% / 3.2% / 3.3%</t>
+          <t>2.9% / 3.1% / 3.2%</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>14.6% / 13.3% / 12.6%</t>
+          <t>13.1% / 12.0% / 11.4%</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>1.5% / 1.4% / 1.4%</t>
+          <t>1.4% / 1.4% / 1.4%</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>0.5% / 0.5% / 0.5%</t>
+          <t>0.4% / 0.4% / 0.5%</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>0.7% / 0.8% / 0.9%</t>
+          <t>0.6% / 0.7% / 0.7%</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>8.1% / 8.7% / 9.0%</t>
+          <t>11.3% / 12.2% / 12.7%</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
-          <t>11.4% / 14.4% / 16.0%</t>
+          <t>8.7% / 11.1% / 12.3%</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>100.5 de 207</t>
+          <t>100.7 de 207</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>139.6 de 207</t>
+          <t>139.9 de 207</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>✓ 67%</t>
+          <t>✓ 68%</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>173.0 de 207</t>
+          <t>173.5 de 207</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>78.8% da capacidade mensal</t>
+          <t>78.4% da capacidade mensal</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>R$ 477.697</t>
+          <t>R$ 476.475</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
